--- a/foundational_documents/former/DOT_signal_dictionary.xlsx
+++ b/foundational_documents/former/DOT_signal_dictionary.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -146,6 +151,8 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2582,6 +2589,103 @@
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Volume_Ratio_10:lo + Micro_RollProxy:lo + Volume:hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE GAP ENTRIES (S.20) — lone-variable conviction; size book longs + fill gaps</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="15" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="15" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Trend-persistence extreme: the D2D long is a genuinely running trend — sizes book longs to 2x AND fires solo when the book is flat</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Micro_Hurst:hi@p97 · D2D+ (LOCK=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Failed break-down reverts upward: confirms the longs that follow AND fires a reversion-long in the gaps the book misses</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Micro_FailedBreak:hi@p90 · D2D- (LOCK=3)</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4460,6 +4564,78 @@
       </c>
       <c r="H51" s="9" t="n">
         <v>7.63</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Failed break-down reversion long; fills book gaps (S.20)</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Trend-persistence long; sizes book longs 2x + gap-fills (S.20)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4953,6 +5129,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>single-variable gap entry (S.20): fires only when zero Dots positions open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
